--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3929" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3929" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:12:34+00:00</t>
+    <t>2026-03-27T13:20:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,6 +514,9 @@
     <t>Support human navigation and code generation.</t>
   </si>
   <si>
+    <t>RUIM eeprescription</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-0
 </t>
   </si>
@@ -528,6 +531,9 @@
   </si>
   <si>
     <t>This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
+  </si>
+  <si>
+    <t>RUIM - european eprescription</t>
   </si>
   <si>
     <t>CodeSystem.status</t>
@@ -3163,7 +3169,7 @@
         <v>75</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="U14" t="s" s="2">
         <v>75</v>
@@ -3211,7 +3217,7 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>95</v>
@@ -3222,10 +3228,10 @@
         <v>3</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3233,7 +3239,7 @@
       </c>
       <c r="F15" s="2"/>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3251,13 +3257,13 @@
         <v>151</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P15" s="2"/>
       <c r="Q15" t="s" s="2">
@@ -3268,7 +3274,7 @@
         <v>75</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="U15" t="s" s="2">
         <v>75</v>
@@ -3307,7 +3313,7 @@
         <v>75</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>80</v>
@@ -3327,10 +3333,10 @@
         <v>3</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" t="s" s="2">
@@ -3356,13 +3362,13 @@
         <v>103</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P16" s="2"/>
       <c r="Q16" t="s" s="2">
@@ -3388,13 +3394,13 @@
         <v>75</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AB16" t="s" s="2">
         <v>75</v>
@@ -3412,7 +3418,7 @@
         <v>75</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>76</v>
@@ -3432,10 +3438,10 @@
         <v>3</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" t="s" s="2">
@@ -3458,19 +3464,19 @@
         <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q17" t="s" s="2">
         <v>75</v>
@@ -3519,7 +3525,7 @@
         <v>75</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>80</v>
@@ -3539,14 +3545,14 @@
         <v>3</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" t="s" s="2">
@@ -3565,16 +3571,16 @@
         <v>84</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" t="s" s="2">
@@ -3624,7 +3630,7 @@
         <v>75</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>80</v>
@@ -3644,14 +3650,14 @@
         <v>3</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" t="s" s="2">
@@ -3673,16 +3679,16 @@
         <v>151</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P19" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q19" t="s" s="2">
         <v>75</v>
@@ -3731,7 +3737,7 @@
         <v>75</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>80</v>
@@ -3751,10 +3757,10 @@
         <v>3</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
@@ -3777,16 +3783,16 @@
         <v>84</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P20" s="2"/>
       <c r="Q20" t="s" s="2">
@@ -3836,7 +3842,7 @@
         <v>75</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>80</v>
@@ -3856,14 +3862,14 @@
         <v>3</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" t="s" s="2">
@@ -3882,16 +3888,16 @@
         <v>75</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="P21" s="2"/>
       <c r="Q21" t="s" s="2">
@@ -3941,7 +3947,7 @@
         <v>75</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>80</v>
@@ -3961,10 +3967,10 @@
         <v>3</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" t="s" s="2">
@@ -3987,19 +3993,19 @@
         <v>84</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P22" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q22" t="s" s="2">
         <v>75</v>
@@ -4048,7 +4054,7 @@
         <v>75</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>80</v>
@@ -4068,10 +4074,10 @@
         <v>3</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
@@ -4094,16 +4100,16 @@
         <v>84</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P23" s="2"/>
       <c r="Q23" t="s" s="2">
@@ -4129,13 +4135,13 @@
         <v>75</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AB23" t="s" s="2">
         <v>75</v>
@@ -4153,7 +4159,7 @@
         <v>75</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>80</v>
@@ -4173,10 +4179,10 @@
         <v>3</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" t="s" s="2">
@@ -4199,16 +4205,16 @@
         <v>75</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" t="s" s="2">
@@ -4258,7 +4264,7 @@
         <v>75</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>80</v>
@@ -4278,14 +4284,14 @@
         <v>3</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" t="s" s="2">
@@ -4304,19 +4310,19 @@
         <v>75</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q25" t="s" s="2">
         <v>75</v>
@@ -4365,7 +4371,7 @@
         <v>75</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>80</v>
@@ -4385,10 +4391,10 @@
         <v>3</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" t="s" s="2">
@@ -4411,16 +4417,16 @@
         <v>84</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" t="s" s="2">
@@ -4470,7 +4476,7 @@
         <v>75</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>80</v>
@@ -4490,10 +4496,10 @@
         <v>3</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" t="s" s="2">
@@ -4516,16 +4522,16 @@
         <v>84</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" t="s" s="2">
@@ -4575,7 +4581,7 @@
         <v>75</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>80</v>
@@ -4595,10 +4601,10 @@
         <v>3</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" t="s" s="2">
@@ -4624,13 +4630,13 @@
         <v>103</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" t="s" s="2">
@@ -4656,13 +4662,13 @@
         <v>75</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AB28" t="s" s="2">
         <v>75</v>
@@ -4680,7 +4686,7 @@
         <v>75</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>80</v>
@@ -4700,14 +4706,14 @@
         <v>3</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" t="s" s="2">
@@ -4726,16 +4732,16 @@
         <v>84</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" t="s" s="2">
@@ -4785,7 +4791,7 @@
         <v>75</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>80</v>
@@ -4805,10 +4811,10 @@
         <v>3</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -4831,16 +4837,16 @@
         <v>84</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -4890,7 +4896,7 @@
         <v>75</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>80</v>
@@ -4910,10 +4916,10 @@
         <v>3</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -4939,10 +4945,10 @@
         <v>103</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" s="2"/>
@@ -4969,13 +4975,13 @@
         <v>75</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AB31" t="s" s="2">
         <v>75</v>
@@ -4993,7 +4999,7 @@
         <v>75</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>76</v>
@@ -5013,10 +5019,10 @@
         <v>3</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5039,16 +5045,16 @@
         <v>84</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5098,7 +5104,7 @@
         <v>75</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>80</v>
@@ -5118,10 +5124,10 @@
         <v>3</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5144,16 +5150,16 @@
         <v>84</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -5203,7 +5209,7 @@
         <v>75</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>80</v>
@@ -5223,10 +5229,10 @@
         <v>3</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -5249,16 +5255,16 @@
         <v>84</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
@@ -5308,7 +5314,7 @@
         <v>75</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -5328,10 +5334,10 @@
         <v>3</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -5357,10 +5363,10 @@
         <v>151</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -5411,7 +5417,7 @@
         <v>75</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>80</v>
@@ -5431,10 +5437,10 @@
         <v>3</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -5463,7 +5469,7 @@
         <v>128</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>130</v>
@@ -5516,7 +5522,7 @@
         <v>75</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>80</v>
@@ -5536,14 +5542,14 @@
         <v>3</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" t="s" s="2">
@@ -5565,10 +5571,10 @@
         <v>127</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>130</v>
@@ -5623,7 +5629,7 @@
         <v>75</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>80</v>
@@ -5643,10 +5649,10 @@
         <v>3</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -5672,10 +5678,10 @@
         <v>103</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -5726,7 +5732,7 @@
         <v>75</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>76</v>
@@ -5746,10 +5752,10 @@
         <v>3</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -5775,10 +5781,10 @@
         <v>151</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -5829,7 +5835,7 @@
         <v>75</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>80</v>
@@ -5849,10 +5855,10 @@
         <v>3</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -5878,10 +5884,10 @@
         <v>103</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -5908,13 +5914,13 @@
         <v>75</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AB40" t="s" s="2">
         <v>75</v>
@@ -5932,7 +5938,7 @@
         <v>75</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>76</v>
@@ -5952,10 +5958,10 @@
         <v>3</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -5981,10 +5987,10 @@
         <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
@@ -6035,7 +6041,7 @@
         <v>75</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>76</v>
@@ -6055,10 +6061,10 @@
         <v>3</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6081,13 +6087,13 @@
         <v>84</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -6126,17 +6132,17 @@
         <v>75</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AD42" s="2"/>
       <c r="AE42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>80</v>
@@ -6156,10 +6162,10 @@
         <v>3</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -6185,10 +6191,10 @@
         <v>151</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" s="2"/>
@@ -6239,7 +6245,7 @@
         <v>75</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>80</v>
@@ -6259,10 +6265,10 @@
         <v>3</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -6291,7 +6297,7 @@
         <v>128</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O44" t="s" s="2">
         <v>130</v>
@@ -6344,7 +6350,7 @@
         <v>75</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>80</v>
@@ -6364,14 +6370,14 @@
         <v>3</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" t="s" s="2">
@@ -6393,10 +6399,10 @@
         <v>127</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O45" t="s" s="2">
         <v>130</v>
@@ -6451,7 +6457,7 @@
         <v>75</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>80</v>
@@ -6471,10 +6477,10 @@
         <v>3</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -6500,10 +6506,10 @@
         <v>103</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
@@ -6530,11 +6536,11 @@
         <v>75</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z46" s="2"/>
       <c r="AA46" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB46" t="s" s="2">
         <v>75</v>
@@ -6552,7 +6558,7 @@
         <v>75</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>76</v>
@@ -6572,10 +6578,10 @@
         <v>3</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -6601,10 +6607,10 @@
         <v>97</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -6655,7 +6661,7 @@
         <v>75</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>80</v>
@@ -6675,10 +6681,10 @@
         <v>3</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -6704,10 +6710,10 @@
         <v>151</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" s="2"/>
@@ -6758,7 +6764,7 @@
         <v>75</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>80</v>
@@ -6778,10 +6784,10 @@
         <v>3</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -6807,10 +6813,10 @@
         <v>103</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
@@ -6837,13 +6843,13 @@
         <v>75</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA49" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB49" t="s" s="2">
         <v>75</v>
@@ -6861,7 +6867,7 @@
         <v>75</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>76</v>
@@ -6881,13 +6887,13 @@
         <v>3</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E50" t="s" s="2">
         <v>75</v>
@@ -6909,13 +6915,13 @@
         <v>84</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
@@ -6966,7 +6972,7 @@
         <v>75</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>80</v>
@@ -6986,10 +6992,10 @@
         <v>3</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7015,10 +7021,10 @@
         <v>151</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
@@ -7069,7 +7075,7 @@
         <v>75</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7095,10 @@
         <v>3</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7121,7 +7127,7 @@
         <v>128</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>130</v>
@@ -7174,7 +7180,7 @@
         <v>75</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>80</v>
@@ -7194,14 +7200,14 @@
         <v>3</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" t="s" s="2">
@@ -7223,10 +7229,10 @@
         <v>127</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O53" t="s" s="2">
         <v>130</v>
@@ -7281,7 +7287,7 @@
         <v>75</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>80</v>
@@ -7301,10 +7307,10 @@
         <v>3</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7330,10 +7336,10 @@
         <v>103</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" s="2"/>
@@ -7345,7 +7351,7 @@
         <v>75</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>75</v>
@@ -7360,11 +7366,11 @@
         <v>75</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z54" s="2"/>
       <c r="AA54" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB54" t="s" s="2">
         <v>75</v>
@@ -7382,7 +7388,7 @@
         <v>75</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>76</v>
@@ -7402,10 +7408,10 @@
         <v>3</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7431,10 +7437,10 @@
         <v>97</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
@@ -7446,7 +7452,7 @@
         <v>75</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>75</v>
@@ -7485,7 +7491,7 @@
         <v>75</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>80</v>
@@ -7505,10 +7511,10 @@
         <v>3</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -7534,10 +7540,10 @@
         <v>151</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" s="2"/>
@@ -7588,7 +7594,7 @@
         <v>75</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>80</v>
@@ -7608,10 +7614,10 @@
         <v>3</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -7637,10 +7643,10 @@
         <v>103</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -7652,7 +7658,7 @@
         <v>75</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>75</v>
@@ -7667,13 +7673,13 @@
         <v>75</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB57" t="s" s="2">
         <v>75</v>
@@ -7691,7 +7697,7 @@
         <v>75</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>76</v>
@@ -7711,13 +7717,13 @@
         <v>3</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E58" t="s" s="2">
         <v>75</v>
@@ -7739,13 +7745,13 @@
         <v>84</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" s="2"/>
@@ -7796,7 +7802,7 @@
         <v>75</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>80</v>
@@ -7816,10 +7822,10 @@
         <v>3</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -7845,10 +7851,10 @@
         <v>151</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
@@ -7899,7 +7905,7 @@
         <v>75</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>80</v>
@@ -7919,10 +7925,10 @@
         <v>3</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -7951,7 +7957,7 @@
         <v>128</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O60" t="s" s="2">
         <v>130</v>
@@ -8004,7 +8010,7 @@
         <v>75</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>80</v>
@@ -8024,14 +8030,14 @@
         <v>3</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" t="s" s="2">
@@ -8053,10 +8059,10 @@
         <v>127</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>130</v>
@@ -8111,7 +8117,7 @@
         <v>75</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>80</v>
@@ -8131,10 +8137,10 @@
         <v>3</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8160,10 +8166,10 @@
         <v>103</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -8175,7 +8181,7 @@
         <v>75</v>
       </c>
       <c r="T62" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="U62" t="s" s="2">
         <v>75</v>
@@ -8190,11 +8196,11 @@
         <v>75</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z62" s="2"/>
       <c r="AA62" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB62" t="s" s="2">
         <v>75</v>
@@ -8212,7 +8218,7 @@
         <v>75</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>76</v>
@@ -8232,10 +8238,10 @@
         <v>3</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -8261,10 +8267,10 @@
         <v>97</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
@@ -8276,7 +8282,7 @@
         <v>75</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>75</v>
@@ -8315,7 +8321,7 @@
         <v>75</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>80</v>
@@ -8335,10 +8341,10 @@
         <v>3</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -8364,10 +8370,10 @@
         <v>151</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" s="2"/>
@@ -8418,7 +8424,7 @@
         <v>75</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>80</v>
@@ -8438,10 +8444,10 @@
         <v>3</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -8467,10 +8473,10 @@
         <v>103</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" s="2"/>
@@ -8482,7 +8488,7 @@
         <v>75</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>75</v>
@@ -8497,13 +8503,13 @@
         <v>75</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA65" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB65" t="s" s="2">
         <v>75</v>
@@ -8521,7 +8527,7 @@
         <v>75</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>76</v>
@@ -8541,13 +8547,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E66" t="s" s="2">
         <v>75</v>
@@ -8569,13 +8575,13 @@
         <v>84</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" s="2"/>
@@ -8626,7 +8632,7 @@
         <v>75</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>80</v>
@@ -8646,10 +8652,10 @@
         <v>3</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -8675,10 +8681,10 @@
         <v>151</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
@@ -8729,7 +8735,7 @@
         <v>75</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>80</v>
@@ -8749,10 +8755,10 @@
         <v>3</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -8781,7 +8787,7 @@
         <v>128</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>130</v>
@@ -8834,7 +8840,7 @@
         <v>75</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>80</v>
@@ -8854,14 +8860,14 @@
         <v>3</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" t="s" s="2">
@@ -8883,10 +8889,10 @@
         <v>127</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>130</v>
@@ -8941,7 +8947,7 @@
         <v>75</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>80</v>
@@ -8961,10 +8967,10 @@
         <v>3</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -8990,10 +8996,10 @@
         <v>103</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" s="2"/>
@@ -9005,7 +9011,7 @@
         <v>75</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>75</v>
@@ -9020,11 +9026,11 @@
         <v>75</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z70" s="2"/>
       <c r="AA70" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB70" t="s" s="2">
         <v>75</v>
@@ -9042,7 +9048,7 @@
         <v>75</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>76</v>
@@ -9062,10 +9068,10 @@
         <v>3</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9091,10 +9097,10 @@
         <v>97</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" s="2"/>
@@ -9106,7 +9112,7 @@
         <v>75</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>75</v>
@@ -9145,7 +9151,7 @@
         <v>75</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>80</v>
@@ -9165,10 +9171,10 @@
         <v>3</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -9194,10 +9200,10 @@
         <v>151</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" s="2"/>
@@ -9248,7 +9254,7 @@
         <v>75</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>80</v>
@@ -9268,10 +9274,10 @@
         <v>3</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -9297,10 +9303,10 @@
         <v>103</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
@@ -9312,7 +9318,7 @@
         <v>75</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>75</v>
@@ -9327,13 +9333,13 @@
         <v>75</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA73" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB73" t="s" s="2">
         <v>75</v>
@@ -9351,7 +9357,7 @@
         <v>75</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>76</v>
@@ -9371,13 +9377,13 @@
         <v>3</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E74" t="s" s="2">
         <v>75</v>
@@ -9399,13 +9405,13 @@
         <v>84</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
@@ -9456,7 +9462,7 @@
         <v>75</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>80</v>
@@ -9476,10 +9482,10 @@
         <v>3</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -9505,10 +9511,10 @@
         <v>151</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" s="2"/>
@@ -9559,7 +9565,7 @@
         <v>75</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>80</v>
@@ -9579,10 +9585,10 @@
         <v>3</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -9611,7 +9617,7 @@
         <v>128</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>130</v>
@@ -9664,7 +9670,7 @@
         <v>75</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>80</v>
@@ -9684,14 +9690,14 @@
         <v>3</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F77" s="2"/>
       <c r="G77" t="s" s="2">
@@ -9713,10 +9719,10 @@
         <v>127</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>130</v>
@@ -9771,7 +9777,7 @@
         <v>75</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH77" t="s" s="2">
         <v>80</v>
@@ -9791,10 +9797,10 @@
         <v>3</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -9820,10 +9826,10 @@
         <v>103</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
@@ -9835,7 +9841,7 @@
         <v>75</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>75</v>
@@ -9850,11 +9856,11 @@
         <v>75</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z78" s="2"/>
       <c r="AA78" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB78" t="s" s="2">
         <v>75</v>
@@ -9872,7 +9878,7 @@
         <v>75</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>76</v>
@@ -9892,10 +9898,10 @@
         <v>3</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -9921,10 +9927,10 @@
         <v>97</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" s="2"/>
@@ -9936,7 +9942,7 @@
         <v>75</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>75</v>
@@ -9975,7 +9981,7 @@
         <v>75</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>80</v>
@@ -9995,10 +10001,10 @@
         <v>3</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10024,10 +10030,10 @@
         <v>151</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" s="2"/>
@@ -10078,7 +10084,7 @@
         <v>75</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>80</v>
@@ -10098,10 +10104,10 @@
         <v>3</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -10127,10 +10133,10 @@
         <v>103</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" s="2"/>
@@ -10142,7 +10148,7 @@
         <v>75</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>75</v>
@@ -10157,13 +10163,13 @@
         <v>75</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA81" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB81" t="s" s="2">
         <v>75</v>
@@ -10181,7 +10187,7 @@
         <v>75</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>76</v>
@@ -10201,13 +10207,13 @@
         <v>3</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E82" t="s" s="2">
         <v>75</v>
@@ -10229,13 +10235,13 @@
         <v>84</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
@@ -10286,7 +10292,7 @@
         <v>75</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>80</v>
@@ -10306,10 +10312,10 @@
         <v>3</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
@@ -10335,10 +10341,10 @@
         <v>151</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" s="2"/>
@@ -10389,7 +10395,7 @@
         <v>75</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>80</v>
@@ -10409,10 +10415,10 @@
         <v>3</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
@@ -10441,7 +10447,7 @@
         <v>128</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>130</v>
@@ -10494,7 +10500,7 @@
         <v>75</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>80</v>
@@ -10514,14 +10520,14 @@
         <v>3</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
@@ -10543,10 +10549,10 @@
         <v>127</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O85" t="s" s="2">
         <v>130</v>
@@ -10601,7 +10607,7 @@
         <v>75</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>80</v>
@@ -10621,10 +10627,10 @@
         <v>3</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -10650,10 +10656,10 @@
         <v>103</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
@@ -10665,7 +10671,7 @@
         <v>75</v>
       </c>
       <c r="T86" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="U86" t="s" s="2">
         <v>75</v>
@@ -10680,11 +10686,11 @@
         <v>75</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z86" s="2"/>
       <c r="AA86" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB86" t="s" s="2">
         <v>75</v>
@@ -10702,7 +10708,7 @@
         <v>75</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -10722,10 +10728,10 @@
         <v>3</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -10751,10 +10757,10 @@
         <v>97</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" s="2"/>
@@ -10766,7 +10772,7 @@
         <v>75</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>75</v>
@@ -10805,7 +10811,7 @@
         <v>75</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>80</v>
@@ -10825,10 +10831,10 @@
         <v>3</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -10854,10 +10860,10 @@
         <v>151</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
@@ -10908,7 +10914,7 @@
         <v>75</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>80</v>
@@ -10928,10 +10934,10 @@
         <v>3</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -10957,10 +10963,10 @@
         <v>103</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
@@ -10972,7 +10978,7 @@
         <v>75</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>75</v>
@@ -10987,13 +10993,13 @@
         <v>75</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA89" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB89" t="s" s="2">
         <v>75</v>
@@ -11011,7 +11017,7 @@
         <v>75</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>76</v>
@@ -11031,13 +11037,13 @@
         <v>3</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E90" t="s" s="2">
         <v>75</v>
@@ -11059,13 +11065,13 @@
         <v>84</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" s="2"/>
@@ -11116,7 +11122,7 @@
         <v>75</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>80</v>
@@ -11136,10 +11142,10 @@
         <v>3</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -11165,10 +11171,10 @@
         <v>151</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -11219,7 +11225,7 @@
         <v>75</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>80</v>
@@ -11239,10 +11245,10 @@
         <v>3</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -11271,7 +11277,7 @@
         <v>128</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>130</v>
@@ -11324,7 +11330,7 @@
         <v>75</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>80</v>
@@ -11344,14 +11350,14 @@
         <v>3</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" t="s" s="2">
@@ -11373,10 +11379,10 @@
         <v>127</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O93" t="s" s="2">
         <v>130</v>
@@ -11431,7 +11437,7 @@
         <v>75</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>80</v>
@@ -11451,10 +11457,10 @@
         <v>3</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -11480,10 +11486,10 @@
         <v>103</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -11495,7 +11501,7 @@
         <v>75</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>75</v>
@@ -11510,11 +11516,11 @@
         <v>75</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z94" s="2"/>
       <c r="AA94" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AB94" t="s" s="2">
         <v>75</v>
@@ -11532,7 +11538,7 @@
         <v>75</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>76</v>
@@ -11552,10 +11558,10 @@
         <v>3</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -11581,10 +11587,10 @@
         <v>97</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" s="2"/>
@@ -11596,7 +11602,7 @@
         <v>75</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>75</v>
@@ -11635,7 +11641,7 @@
         <v>75</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>80</v>
@@ -11655,10 +11661,10 @@
         <v>3</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -11684,10 +11690,10 @@
         <v>151</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" s="2"/>
@@ -11738,7 +11744,7 @@
         <v>75</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>80</v>
@@ -11758,10 +11764,10 @@
         <v>3</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -11787,10 +11793,10 @@
         <v>103</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" s="2"/>
@@ -11802,7 +11808,7 @@
         <v>75</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>75</v>
@@ -11817,13 +11823,13 @@
         <v>75</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA97" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AB97" t="s" s="2">
         <v>75</v>
@@ -11841,7 +11847,7 @@
         <v>75</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>76</v>
@@ -11861,10 +11867,10 @@
         <v>3</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -11887,16 +11893,16 @@
         <v>75</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P98" s="2"/>
       <c r="Q98" t="s" s="2">
@@ -11946,7 +11952,7 @@
         <v>75</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>80</v>
@@ -11966,10 +11972,10 @@
         <v>3</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -11995,10 +12001,10 @@
         <v>151</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -12049,7 +12055,7 @@
         <v>75</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>80</v>
@@ -12069,10 +12075,10 @@
         <v>3</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -12101,7 +12107,7 @@
         <v>128</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>130</v>
@@ -12154,7 +12160,7 @@
         <v>75</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>80</v>
@@ -12174,14 +12180,14 @@
         <v>3</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" t="s" s="2">
@@ -12203,10 +12209,10 @@
         <v>127</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O101" t="s" s="2">
         <v>130</v>
@@ -12261,7 +12267,7 @@
         <v>75</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>80</v>
@@ -12281,10 +12287,10 @@
         <v>3</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -12310,10 +12316,10 @@
         <v>103</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -12364,7 +12370,7 @@
         <v>75</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>76</v>
@@ -12384,10 +12390,10 @@
         <v>3</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -12413,10 +12419,10 @@
         <v>151</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" s="2"/>
@@ -12467,7 +12473,7 @@
         <v>75</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>80</v>
@@ -12487,10 +12493,10 @@
         <v>3</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -12516,10 +12522,10 @@
         <v>151</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -12570,7 +12576,7 @@
         <v>75</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>80</v>
@@ -12590,10 +12596,10 @@
         <v>3</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -12616,19 +12622,19 @@
         <v>75</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P105" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q105" t="s" s="2">
         <v>75</v>
@@ -12677,7 +12683,7 @@
         <v>75</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>80</v>
@@ -12697,10 +12703,10 @@
         <v>3</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -12726,10 +12732,10 @@
         <v>151</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -12780,7 +12786,7 @@
         <v>75</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>80</v>
@@ -12800,10 +12806,10 @@
         <v>3</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -12832,7 +12838,7 @@
         <v>128</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>130</v>
@@ -12885,7 +12891,7 @@
         <v>75</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>80</v>
@@ -12905,14 +12911,14 @@
         <v>3</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" t="s" s="2">
@@ -12934,10 +12940,10 @@
         <v>127</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>130</v>
@@ -12992,7 +12998,7 @@
         <v>75</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>80</v>
@@ -13012,10 +13018,10 @@
         <v>3</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -13041,13 +13047,13 @@
         <v>103</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" t="s" s="2">
@@ -13097,7 +13103,7 @@
         <v>75</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>80</v>
@@ -13117,10 +13123,10 @@
         <v>3</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -13143,16 +13149,16 @@
         <v>75</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
@@ -13178,13 +13184,13 @@
         <v>75</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA110" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AB110" t="s" s="2">
         <v>75</v>
@@ -13202,7 +13208,7 @@
         <v>75</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>80</v>
@@ -13222,10 +13228,10 @@
         <v>3</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -13251,10 +13257,10 @@
         <v>151</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" s="2"/>
@@ -13305,7 +13311,7 @@
         <v>75</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -13325,10 +13331,10 @@
         <v>3</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -13351,13 +13357,13 @@
         <v>75</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" s="2"/>
@@ -13408,7 +13414,7 @@
         <v>75</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>80</v>
@@ -13428,10 +13434,10 @@
         <v>3</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -13457,10 +13463,10 @@
         <v>151</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" s="2"/>
@@ -13511,7 +13517,7 @@
         <v>75</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>80</v>
@@ -13531,10 +13537,10 @@
         <v>3</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -13563,7 +13569,7 @@
         <v>128</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>130</v>
@@ -13616,7 +13622,7 @@
         <v>75</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>80</v>
@@ -13636,14 +13642,14 @@
         <v>3</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
@@ -13665,10 +13671,10 @@
         <v>127</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O115" t="s" s="2">
         <v>130</v>
@@ -13723,7 +13729,7 @@
         <v>75</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>80</v>
@@ -13743,10 +13749,10 @@
         <v>3</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -13772,10 +13778,10 @@
         <v>103</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" s="2"/>
@@ -13826,7 +13832,7 @@
         <v>75</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>76</v>
@@ -13846,10 +13852,10 @@
         <v>3</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -13872,13 +13878,13 @@
         <v>75</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
@@ -13929,7 +13935,7 @@
         <v>75</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>76</v>
@@ -13949,10 +13955,10 @@
         <v>3</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -13978,10 +13984,10 @@
         <v>77</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
@@ -14032,7 +14038,7 @@
         <v>75</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AH118" t="s" s="2">
         <v>80</v>

--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:20:16+00:00</t>
+    <t>2026-03-30T07:06:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:06:10+00:00</t>
+    <t>2026-03-30T07:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1723,7 +1723,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="59.74609375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="136.359375" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="8.53515625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
@@ -7555,7 +7555,7 @@
         <v>75</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>75</v>
+        <v>322</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>75</v>
@@ -8385,7 +8385,7 @@
         <v>75</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>75</v>
+        <v>335</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>75</v>
@@ -9215,7 +9215,7 @@
         <v>75</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>75</v>
+        <v>347</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>75</v>
@@ -10045,7 +10045,7 @@
         <v>75</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>75</v>
+        <v>359</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>75</v>
@@ -10875,7 +10875,7 @@
         <v>75</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>75</v>
@@ -11705,7 +11705,7 @@
         <v>75</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>75</v>
+        <v>383</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>75</v>

--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:17:30+00:00</t>
+    <t>2026-03-30T07:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:19:25+00:00</t>
+    <t>2026-03-30T13:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:31:48+00:00</t>
+    <t>2026-03-30T13:39:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -975,7 +975,7 @@
     <t>A code that is used to identify the property. The code is used internally (in CodeSystem.concept.property.code) and also externally, such as in property filters.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/ruim/ValueSet/vs-ruim-property-codes|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/ruim/ValueSet/vs-ruim-property-codes|0.0.1</t>
   </si>
   <si>
     <t>CodeSystem.property.uri</t>

--- a/nriss-patch-1/ig/all-profiles.xlsx
+++ b/nriss-patch-1/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:39:05+00:00</t>
+    <t>2026-03-30T13:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
